--- a/tests/fixtures/sumprod_z1_2026-04-11.xlsx
+++ b/tests/fixtures/sumprod_z1_2026-04-11.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="invalid_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="valid_data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="calc_data" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="output" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sumprod_df" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="invalid_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="valid_data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="calc_data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="output" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1452,327 +1453,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>idx</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>concept</t>
+          <t>idx_from</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>pertype</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>idx_from</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>idx</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>period</t>
+          <t>sump_coef</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>q2019-4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>q2019-4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>q2019-4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
+      <c r="C3" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>q2019-4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
+      <c r="C5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>q2019-4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>q2020-1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
+      <c r="C7" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>q2020-4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>q2020-4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>q2021-2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>q2021-2</t>
-        </is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>q2020-4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>q2021-3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>q2021-3</t>
         </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1786,813 +1799,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>idx</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>concept</t>
+          <t>idx_from</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pertype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>qrtr_target</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>rolly_target</t>
+          <t>sump_coef</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2019-4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>q2019-4</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>160</v>
-      </c>
-      <c r="F2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G2" t="n">
-        <v>160</v>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>220</v>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>125</v>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>205</v>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>156</v>
-      </c>
-      <c r="F5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G5" t="n">
-        <v>196</v>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q2020-4</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>195</v>
-      </c>
-      <c r="F6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G6" t="n">
-        <v>195</v>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>125</v>
-      </c>
-      <c r="F7" t="n">
-        <v>125</v>
-      </c>
-      <c r="G7" t="n">
-        <v>220</v>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q2021-2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" t="n">
-        <v>31</v>
-      </c>
-      <c r="G8" t="n">
-        <v>226</v>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q2021-3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>195</v>
-      </c>
-      <c r="F9" t="n">
-        <v>39</v>
-      </c>
-      <c r="G9" t="n">
-        <v>234</v>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q2021-4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>244</v>
-      </c>
-      <c r="F10" t="n">
-        <v>49</v>
-      </c>
-      <c r="G10" t="n">
-        <v>244</v>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>q2022-1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>150</v>
-      </c>
-      <c r="F11" t="n">
-        <v>150</v>
-      </c>
-      <c r="G11" t="n">
-        <v>269</v>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>q2019-4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>120</v>
-      </c>
-      <c r="F12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" t="n">
-        <v>120</v>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>70</v>
-      </c>
-      <c r="F13" t="n">
-        <v>70</v>
-      </c>
-      <c r="G13" t="n">
-        <v>160</v>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>88</v>
-      </c>
-      <c r="F14" t="n">
-        <v>18</v>
-      </c>
-      <c r="G14" t="n">
-        <v>148</v>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>110</v>
-      </c>
-      <c r="F15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G15" t="n">
-        <v>140</v>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>q2020-4</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>138</v>
-      </c>
-      <c r="F16" t="n">
-        <v>28</v>
-      </c>
-      <c r="G16" t="n">
-        <v>138</v>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
           <t>q2021-1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
-      <c r="F17" t="n">
-        <v>100</v>
-      </c>
-      <c r="G17" t="n">
-        <v>168</v>
+      <c r="C17" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
           <t>q2021-2</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>125</v>
-      </c>
-      <c r="F18" t="n">
-        <v>25</v>
-      </c>
-      <c r="G18" t="n">
-        <v>175</v>
+      <c r="C18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
           <t>q2021-3</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>156</v>
-      </c>
-      <c r="F19" t="n">
-        <v>31</v>
-      </c>
-      <c r="G19" t="n">
-        <v>184</v>
+      <c r="C19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>q2021-4</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>195</v>
-      </c>
-      <c r="F20" t="n">
-        <v>39</v>
-      </c>
-      <c r="G20" t="n">
-        <v>195</v>
+      <c r="C20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>q2022-1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>125</v>
-      </c>
-      <c r="F21" t="n">
-        <v>125</v>
-      </c>
-      <c r="G21" t="n">
-        <v>220</v>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cieA</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>costs</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>q2022-2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>156</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>q2020-4</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>195</v>
-      </c>
-      <c r="F23" t="n">
-        <v>39</v>
-      </c>
-      <c r="G23" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>q2021-2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>156</v>
-      </c>
-      <c r="F24" t="n">
-        <v>31</v>
-      </c>
-      <c r="G24" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>q2021-4</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>244</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>q2021-4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>244</v>
-      </c>
-      <c r="F26" t="n">
-        <v>49</v>
-      </c>
-      <c r="G26" t="n">
-        <v>244</v>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2606,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2622,17 +2161,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>pertype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>idx</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>rolly_amt</t>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>qrtr_target</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rolly_target</t>
         </is>
       </c>
     </row>
@@ -2644,21 +2193,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2019-4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>q2019-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -2669,21 +2224,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>q2020-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="4">
@@ -2694,21 +2255,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -2719,21 +2286,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>q2020-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" t="n">
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -2744,21 +2317,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>q2020-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>195</v>
+      </c>
+      <c r="F6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G6" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -2769,21 +2348,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>q2021-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>168</v>
+        <v>125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -2794,21 +2379,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>q2021-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="9">
@@ -2819,21 +2410,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>q2021-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>184</v>
+        <v>195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -2844,21 +2441,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>q2021-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>244</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2869,21 +2472,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>q2022-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220</v>
+        <v>150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G11" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="12">
@@ -2894,21 +2503,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2019-4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>q2019-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>160</v>
+        <v>120</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -2919,21 +2534,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>q2020-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220</v>
+        <v>70</v>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -2944,21 +2565,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205</v>
+        <v>88</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -2969,21 +2596,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>q2020-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>196</v>
+        <v>110</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22</v>
+      </c>
+      <c r="G15" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="16">
@@ -2994,21 +2627,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>q2020-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>138</v>
+      </c>
+      <c r="F16" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -3019,21 +2658,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>q2021-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220</v>
+        <v>100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="18">
@@ -3044,21 +2689,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>q2021-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>226</v>
+        <v>125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="19">
@@ -3069,21 +2720,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>q2021-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>234</v>
+        <v>156</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="20">
@@ -3094,21 +2751,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>q2021-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>244</v>
+        <v>195</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39</v>
+      </c>
+      <c r="G20" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="21">
@@ -3119,47 +2782,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>q2022-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>269</v>
+        <v>125</v>
+      </c>
+      <c r="F21" t="n">
+        <v>125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2022-2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>q2020-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>195</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3174,17 +2845,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>q2021-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>195</v>
       </c>
+      <c r="F23" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3199,16 +2876,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>q2021-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>351</v>
+        <v>156</v>
+      </c>
+      <c r="F24" t="n">
+        <v>31</v>
+      </c>
+      <c r="G24" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="25">
@@ -3224,22 +2907,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>q2021-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>195</v>
+        <v>244</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>244</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>cieC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3249,90 +2936,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>q2021-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>244</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>q2022-1</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>q2021-4</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>q2022-1</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="F26" t="n">
+        <v>49</v>
+      </c>
+      <c r="G26" t="n">
         <v>244</v>
       </c>
     </row>
@@ -3347,6 +2965,747 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pertype</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rolly_amt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
